--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-18</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4693" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4693" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -463,25 +463,29 @@
     <t>The registered place of birth of the patient. A sytem may use the address.text if they don't store the birthPlace address in discrete elements.</t>
   </si>
   <si>
-    <t>Patient.extension:birthPlace.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:birthPlace.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace.extension</t>
   </si>
   <si>
@@ -528,24 +532,16 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Patient.extension:birthPlace.value[x].id</t>
   </si>
   <si>
     <t>Patient.extension.value[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].extension</t>
@@ -825,9 +821,6 @@
     <t>Patient.extension:nationality.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Patient.extension:nationality.extension:code</t>
   </si>
   <si>
@@ -1069,7 +1062,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -3288,7 +3281,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>133</v>
@@ -3299,10 +3292,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -3325,13 +3318,13 @@
         <v>22</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -3382,7 +3375,7 @@
         <v>22</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>76</v>
@@ -3391,7 +3384,7 @@
         <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>22</v>
@@ -3402,10 +3395,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3476,7 +3469,7 @@
         <v>130</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE12" t="s" s="2">
         <v>22</v>
@@ -3485,7 +3478,7 @@
         <v>131</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>76</v>
@@ -3505,10 +3498,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -3534,13 +3527,13 @@
         <v>98</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
@@ -3548,7 +3541,7 @@
       </c>
       <c r="R13" s="2"/>
       <c r="S13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>22</v>
@@ -3590,7 +3583,7 @@
         <v>22</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>84</v>
@@ -3610,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -3636,13 +3629,13 @@
         <v>22</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -3693,7 +3686,7 @@
         <v>22</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>76</v>
@@ -3702,7 +3695,7 @@
         <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>96</v>
@@ -3739,13 +3732,13 @@
         <v>22</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -3796,7 +3789,7 @@
         <v>22</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>76</v>
@@ -3816,14 +3809,14 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" t="s" s="2">
@@ -3845,13 +3838,13 @@
         <v>127</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
@@ -3892,7 +3885,7 @@
         <v>130</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE16" t="s" s="2">
         <v>22</v>
@@ -3901,7 +3894,7 @@
         <v>131</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>76</v>
@@ -3921,10 +3914,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3950,16 +3943,16 @@
         <v>104</v>
       </c>
       <c r="M17" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="O17" t="s" s="2">
+      <c r="P17" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="P17" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="Q17" t="s" s="2">
         <v>22</v>
@@ -3972,43 +3965,43 @@
         <v>22</v>
       </c>
       <c r="U17" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="V17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AA17" t="s" s="2">
+      <c r="AB17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG17" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>76</v>
@@ -4028,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -4057,13 +4050,13 @@
         <v>104</v>
       </c>
       <c r="M18" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -4077,43 +4070,43 @@
         <v>22</v>
       </c>
       <c r="U18" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="V18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AA18" t="s" s="2">
+      <c r="AB18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG18" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>76</v>
@@ -4133,10 +4126,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -4159,19 +4152,19 @@
         <v>85</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O19" t="s" s="2">
+      <c r="P19" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="P19" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="Q19" t="s" s="2">
         <v>22</v>
@@ -4184,43 +4177,43 @@
         <v>22</v>
       </c>
       <c r="U19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>76</v>
@@ -4240,10 +4233,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4266,13 +4259,13 @@
         <v>85</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -4287,43 +4280,43 @@
         <v>22</v>
       </c>
       <c r="U20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
@@ -4343,14 +4336,14 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
@@ -4369,13 +4362,13 @@
         <v>85</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -4390,43 +4383,43 @@
         <v>22</v>
       </c>
       <c r="U21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
@@ -4446,14 +4439,14 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
@@ -4472,16 +4465,16 @@
         <v>85</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
@@ -4495,43 +4488,43 @@
         <v>22</v>
       </c>
       <c r="U22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -4551,14 +4544,14 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
@@ -4577,13 +4570,13 @@
         <v>85</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -4634,7 +4627,7 @@
         <v>22</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
@@ -4654,14 +4647,14 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -4680,13 +4673,13 @@
         <v>85</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -4701,43 +4694,43 @@
         <v>22</v>
       </c>
       <c r="U24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -4757,10 +4750,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4783,16 +4776,16 @@
         <v>85</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
@@ -4842,7 +4835,7 @@
         <v>22</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>76</v>
@@ -4862,10 +4855,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4888,17 +4881,17 @@
         <v>85</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q26" t="s" s="2">
         <v>22</v>
@@ -4911,43 +4904,43 @@
         <v>22</v>
       </c>
       <c r="U26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
@@ -4967,13 +4960,13 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>126</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>22</v>
@@ -4995,13 +4988,13 @@
         <v>22</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -5061,7 +5054,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>133</v>
@@ -5072,10 +5065,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5098,13 +5091,13 @@
         <v>22</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -5155,7 +5148,7 @@
         <v>22</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
@@ -5164,7 +5157,7 @@
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>22</v>
@@ -5175,14 +5168,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -5204,13 +5197,13 @@
         <v>127</v>
       </c>
       <c r="M29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="O29" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
@@ -5251,7 +5244,7 @@
         <v>130</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE29" t="s" s="2">
         <v>22</v>
@@ -5260,7 +5253,7 @@
         <v>131</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5280,13 +5273,13 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>22</v>
@@ -5365,7 +5358,7 @@
         <v>22</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -5385,10 +5378,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5411,13 +5404,13 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -5468,7 +5461,7 @@
         <v>22</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5477,7 +5470,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>22</v>
@@ -5488,10 +5481,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5562,7 +5555,7 @@
         <v>130</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE32" t="s" s="2">
         <v>22</v>
@@ -5571,7 +5564,7 @@
         <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -5591,10 +5584,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5620,13 +5613,13 @@
         <v>98</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -5634,7 +5627,7 @@
       </c>
       <c r="R33" s="2"/>
       <c r="S33" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>22</v>
@@ -5676,7 +5669,7 @@
         <v>22</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>84</v>
@@ -5696,10 +5689,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5722,13 +5715,13 @@
         <v>22</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -5755,11 +5748,11 @@
         <v>22</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z34" s="2"/>
       <c r="AA34" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AB34" t="s" s="2">
         <v>22</v>
@@ -5777,7 +5770,7 @@
         <v>22</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>76</v>
@@ -5786,7 +5779,7 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>96</v>
@@ -5797,10 +5790,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5823,13 +5816,13 @@
         <v>22</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5880,7 +5873,7 @@
         <v>22</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
@@ -5900,14 +5893,14 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
@@ -5929,13 +5922,13 @@
         <v>127</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
@@ -5976,7 +5969,7 @@
         <v>130</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE36" t="s" s="2">
         <v>22</v>
@@ -5985,7 +5978,7 @@
         <v>131</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
@@ -6005,10 +5998,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6031,19 +6024,19 @@
         <v>85</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="P37" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P37" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>22</v>
@@ -6092,7 +6085,7 @@
         <v>22</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
@@ -6112,10 +6105,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6138,13 +6131,13 @@
         <v>22</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6195,7 +6188,7 @@
         <v>22</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6215,14 +6208,14 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
@@ -6244,13 +6237,13 @@
         <v>127</v>
       </c>
       <c r="M39" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
@@ -6291,7 +6284,7 @@
         <v>130</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE39" t="s" s="2">
         <v>22</v>
@@ -6300,7 +6293,7 @@
         <v>131</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
@@ -6320,10 +6313,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6349,16 +6342,16 @@
         <v>98</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="P40" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>22</v>
@@ -6407,7 +6400,7 @@
         <v>22</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -6427,10 +6420,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6453,16 +6446,16 @@
         <v>85</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
@@ -6512,7 +6505,7 @@
         <v>22</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -6532,10 +6525,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6561,14 +6554,14 @@
         <v>104</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q42" t="s" s="2">
         <v>22</v>
@@ -6617,7 +6610,7 @@
         <v>22</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -6637,10 +6630,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6663,17 +6656,17 @@
         <v>85</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q43" t="s" s="2">
         <v>22</v>
@@ -6722,7 +6715,7 @@
         <v>22</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
@@ -6742,10 +6735,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6768,19 +6761,19 @@
         <v>85</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="P44" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>22</v>
@@ -6829,7 +6822,7 @@
         <v>22</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -6849,10 +6842,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6875,19 +6868,19 @@
         <v>85</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="P45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>22</v>
@@ -6936,7 +6929,7 @@
         <v>22</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -6956,13 +6949,13 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E46" t="s" s="2">
         <v>22</v>
@@ -6987,10 +6980,10 @@
         <v>127</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -7041,7 +7034,7 @@
         <v>22</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7061,10 +7054,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7087,13 +7080,13 @@
         <v>22</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7144,7 +7137,7 @@
         <v>22</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7153,7 +7146,7 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>22</v>
@@ -7164,10 +7157,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7238,7 +7231,7 @@
         <v>130</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE48" t="s" s="2">
         <v>22</v>
@@ -7247,7 +7240,7 @@
         <v>131</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7267,10 +7260,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7296,13 +7289,13 @@
         <v>98</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -7310,7 +7303,7 @@
       </c>
       <c r="R49" s="2"/>
       <c r="S49" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>22</v>
@@ -7352,7 +7345,7 @@
         <v>22</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>84</v>
@@ -7372,10 +7365,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7398,13 +7391,13 @@
         <v>22</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
@@ -7455,7 +7448,7 @@
         <v>22</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -7464,7 +7457,7 @@
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>96</v>
@@ -7475,10 +7468,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7504,13 +7497,13 @@
         <v>98</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
@@ -7518,7 +7511,7 @@
       </c>
       <c r="R51" s="2"/>
       <c r="S51" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>22</v>
@@ -7560,7 +7553,7 @@
         <v>22</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>84</v>
@@ -7580,10 +7573,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7606,13 +7599,13 @@
         <v>22</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -7663,7 +7656,7 @@
         <v>22</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
@@ -7672,7 +7665,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>96</v>
@@ -7683,14 +7676,14 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
@@ -7712,16 +7705,16 @@
         <v>127</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="P53" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>22</v>
@@ -7770,7 +7763,7 @@
         <v>22</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -7790,10 +7783,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7816,17 +7809,17 @@
         <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>22</v>
@@ -7875,7 +7868,7 @@
         <v>22</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -7895,10 +7888,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7921,26 +7914,26 @@
         <v>85</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="P55" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="O55" t="s" s="2">
+      <c r="Q55" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="P55" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="Q55" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R55" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="S55" t="s" s="2">
         <v>22</v>
       </c>
@@ -7984,7 +7977,7 @@
         <v>22</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8004,10 +7997,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8030,19 +8023,19 @@
         <v>85</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="P56" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>22</v>
@@ -8091,7 +8084,7 @@
         <v>22</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
@@ -8111,10 +8104,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8137,13 +8130,13 @@
         <v>22</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8194,7 +8187,7 @@
         <v>22</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -8214,14 +8207,14 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" t="s" s="2">
@@ -8243,13 +8236,13 @@
         <v>127</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -8290,7 +8283,7 @@
         <v>130</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE58" t="s" s="2">
         <v>22</v>
@@ -8299,7 +8292,7 @@
         <v>131</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
@@ -8319,10 +8312,10 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8348,16 +8341,16 @@
         <v>104</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="P59" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="Q59" t="s" s="2">
         <v>22</v>
@@ -8382,31 +8375,31 @@
         <v>22</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG59" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -8426,10 +8419,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8452,19 +8445,19 @@
         <v>85</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="P60" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q60" t="s" s="2">
         <v>22</v>
@@ -8513,7 +8506,7 @@
         <v>22</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -8533,14 +8526,14 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
@@ -8559,16 +8552,16 @@
         <v>85</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -8618,7 +8611,7 @@
         <v>22</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
@@ -8638,14 +8631,14 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
@@ -8664,16 +8657,16 @@
         <v>85</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -8723,7 +8716,7 @@
         <v>22</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -8743,10 +8736,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8769,13 +8762,13 @@
         <v>85</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
@@ -8826,7 +8819,7 @@
         <v>22</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
@@ -8846,10 +8839,10 @@
         <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8872,13 +8865,13 @@
         <v>22</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -8929,7 +8922,7 @@
         <v>22</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>76</v>
@@ -8949,10 +8942,10 @@
         <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9030,7 +9023,7 @@
         <v>131</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>76</v>
@@ -9050,13 +9043,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="D66" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>22</v>
@@ -9078,16 +9071,16 @@
         <v>22</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
@@ -9137,7 +9130,7 @@
         <v>22</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>76</v>
@@ -9146,7 +9139,7 @@
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>133</v>
@@ -9157,10 +9150,10 @@
         <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9183,13 +9176,13 @@
         <v>22</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
@@ -9240,7 +9233,7 @@
         <v>22</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>76</v>
@@ -9249,7 +9242,7 @@
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>22</v>
@@ -9260,10 +9253,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9334,7 +9327,7 @@
         <v>130</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE68" t="s" s="2">
         <v>22</v>
@@ -9343,7 +9336,7 @@
         <v>131</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>76</v>
@@ -9363,10 +9356,10 @@
         <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9392,13 +9385,13 @@
         <v>98</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9406,7 +9399,7 @@
       </c>
       <c r="R69" s="2"/>
       <c r="S69" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>22</v>
@@ -9448,7 +9441,7 @@
         <v>22</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>84</v>
@@ -9468,10 +9461,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9497,10 +9490,10 @@
         <v>104</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -9509,7 +9502,7 @@
       </c>
       <c r="R70" s="2"/>
       <c r="S70" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>22</v>
@@ -9527,11 +9520,11 @@
         <v>22</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z70" s="2"/>
       <c r="AA70" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>22</v>
@@ -9549,7 +9542,7 @@
         <v>22</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9558,7 +9551,7 @@
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>96</v>
@@ -9569,10 +9562,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9595,13 +9588,13 @@
         <v>22</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
@@ -9625,7 +9618,7 @@
         <v>22</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y71" t="s" s="2">
         <v>22</v>
@@ -9652,7 +9645,7 @@
         <v>22</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
@@ -9672,10 +9665,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9698,13 +9691,13 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -9755,7 +9748,7 @@
         <v>22</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>76</v>
@@ -9775,10 +9768,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9801,17 +9794,17 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Q73" t="s" s="2">
         <v>22</v>
@@ -9860,7 +9853,7 @@
         <v>22</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -9880,10 +9873,10 @@
         <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -9906,19 +9899,19 @@
         <v>85</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>22</v>
@@ -9967,7 +9960,7 @@
         <v>22</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
@@ -9987,10 +9980,10 @@
         <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10016,16 +10009,16 @@
         <v>104</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="P75" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>22</v>
@@ -10050,13 +10043,13 @@
         <v>22</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AA75" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AB75" t="s" s="2">
         <v>22</v>
@@ -10074,7 +10067,7 @@
         <v>22</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10094,10 +10087,10 @@
         <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10120,19 +10113,19 @@
         <v>85</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="P76" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>22</v>
@@ -10181,7 +10174,7 @@
         <v>22</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
@@ -10201,10 +10194,10 @@
         <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10227,19 +10220,19 @@
         <v>85</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="P77" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>22</v>
@@ -10288,7 +10281,7 @@
         <v>22</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10308,10 +10301,10 @@
         <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10334,19 +10327,19 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="P78" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>22</v>
@@ -10395,7 +10388,7 @@
         <v>22</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -10415,10 +10408,10 @@
         <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10441,13 +10434,13 @@
         <v>22</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10498,7 +10491,7 @@
         <v>22</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>76</v>
@@ -10518,14 +10511,14 @@
         <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" t="s" s="2">
@@ -10547,13 +10540,13 @@
         <v>127</v>
       </c>
       <c r="M80" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
@@ -10594,7 +10587,7 @@
         <v>130</v>
       </c>
       <c r="AD80" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE80" t="s" s="2">
         <v>22</v>
@@ -10603,7 +10596,7 @@
         <v>131</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -10623,10 +10616,10 @@
         <v>3</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10652,16 +10645,16 @@
         <v>104</v>
       </c>
       <c r="M81" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="O81" t="s" s="2">
+      <c r="P81" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>22</v>
@@ -10674,43 +10667,43 @@
         <v>22</v>
       </c>
       <c r="U81" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y81" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="V81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y81" t="s" s="2">
+      <c r="Z81" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Z81" t="s" s="2">
+      <c r="AA81" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AA81" t="s" s="2">
+      <c r="AB81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG81" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10730,10 +10723,10 @@
         <v>3</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10759,13 +10752,13 @@
         <v>104</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" t="s" s="2">
@@ -10779,43 +10772,43 @@
         <v>22</v>
       </c>
       <c r="U82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="V82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AA82" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AA82" t="s" s="2">
+      <c r="AB82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG82" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
@@ -10835,10 +10828,10 @@
         <v>3</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10861,19 +10854,19 @@
         <v>85</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M83" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="O83" t="s" s="2">
+      <c r="P83" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>22</v>
@@ -10886,43 +10879,43 @@
         <v>22</v>
       </c>
       <c r="U83" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG83" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
@@ -10942,10 +10935,10 @@
         <v>3</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10968,13 +10961,13 @@
         <v>85</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M84" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -10989,43 +10982,43 @@
         <v>22</v>
       </c>
       <c r="U84" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG84" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>76</v>
@@ -11045,14 +11038,14 @@
         <v>3</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
@@ -11071,13 +11064,13 @@
         <v>85</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -11092,43 +11085,43 @@
         <v>22</v>
       </c>
       <c r="U85" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG85" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11148,14 +11141,14 @@
         <v>3</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
@@ -11174,16 +11167,16 @@
         <v>85</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M86" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
@@ -11197,43 +11190,43 @@
         <v>22</v>
       </c>
       <c r="U86" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG86" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11253,14 +11246,14 @@
         <v>3</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" t="s" s="2">
@@ -11279,13 +11272,13 @@
         <v>85</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -11336,7 +11329,7 @@
         <v>22</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -11356,14 +11349,14 @@
         <v>3</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
@@ -11382,13 +11375,13 @@
         <v>85</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -11403,43 +11396,43 @@
         <v>22</v>
       </c>
       <c r="U88" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG88" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -11459,10 +11452,10 @@
         <v>3</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11485,16 +11478,16 @@
         <v>85</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -11544,7 +11537,7 @@
         <v>22</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -11564,10 +11557,10 @@
         <v>3</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11590,17 +11583,17 @@
         <v>85</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q90" t="s" s="2">
         <v>22</v>
@@ -11613,43 +11606,43 @@
         <v>22</v>
       </c>
       <c r="U90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG90" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -11669,10 +11662,10 @@
         <v>3</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11695,17 +11688,17 @@
         <v>22</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>22</v>
@@ -11730,13 +11723,13 @@
         <v>22</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>22</v>
@@ -11754,7 +11747,7 @@
         <v>22</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -11774,10 +11767,10 @@
         <v>3</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11800,13 +11793,13 @@
         <v>22</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -11857,7 +11850,7 @@
         <v>22</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -11877,14 +11870,14 @@
         <v>3</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" t="s" s="2">
@@ -11906,13 +11899,13 @@
         <v>127</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
@@ -11953,7 +11946,7 @@
         <v>130</v>
       </c>
       <c r="AD93" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE93" t="s" s="2">
         <v>22</v>
@@ -11962,7 +11955,7 @@
         <v>131</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -11982,10 +11975,10 @@
         <v>3</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12008,19 +12001,19 @@
         <v>85</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="P94" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>22</v>
@@ -12069,7 +12062,7 @@
         <v>22</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -12089,10 +12082,10 @@
         <v>3</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12115,13 +12108,13 @@
         <v>22</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -12172,7 +12165,7 @@
         <v>22</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
@@ -12192,14 +12185,14 @@
         <v>3</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
@@ -12221,13 +12214,13 @@
         <v>127</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P96" s="2"/>
       <c r="Q96" t="s" s="2">
@@ -12268,7 +12261,7 @@
         <v>130</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE96" t="s" s="2">
         <v>22</v>
@@ -12277,7 +12270,7 @@
         <v>131</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -12297,10 +12290,10 @@
         <v>3</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12326,16 +12319,16 @@
         <v>98</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="P97" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>22</v>
@@ -12384,7 +12377,7 @@
         <v>22</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -12404,10 +12397,10 @@
         <v>3</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12430,16 +12423,16 @@
         <v>85</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O98" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -12489,7 +12482,7 @@
         <v>22</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>76</v>
@@ -12509,10 +12502,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12538,14 +12531,14 @@
         <v>104</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q99" t="s" s="2">
         <v>22</v>
@@ -12594,7 +12587,7 @@
         <v>22</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -12614,10 +12607,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12640,17 +12633,17 @@
         <v>85</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q100" t="s" s="2">
         <v>22</v>
@@ -12699,7 +12692,7 @@
         <v>22</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -12719,10 +12712,10 @@
         <v>3</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12745,19 +12738,19 @@
         <v>85</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="P101" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="Q101" t="s" s="2">
         <v>22</v>
@@ -12806,7 +12799,7 @@
         <v>22</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>76</v>
@@ -12826,10 +12819,10 @@
         <v>3</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12852,19 +12845,19 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="P102" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="Q102" t="s" s="2">
         <v>22</v>
@@ -12913,7 +12906,7 @@
         <v>22</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -12933,10 +12926,10 @@
         <v>3</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -12959,19 +12952,19 @@
         <v>22</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="P103" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="Q103" t="s" s="2">
         <v>22</v>
@@ -13020,7 +13013,7 @@
         <v>22</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
@@ -13040,10 +13033,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13066,19 +13059,19 @@
         <v>22</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="P104" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>22</v>
@@ -13127,7 +13120,7 @@
         <v>22</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>76</v>
@@ -13147,10 +13140,10 @@
         <v>3</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13173,19 +13166,19 @@
         <v>22</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="P105" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>22</v>
@@ -13234,7 +13227,7 @@
         <v>22</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
@@ -13246,7 +13239,7 @@
         <v>22</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106">
@@ -13254,10 +13247,10 @@
         <v>3</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13280,13 +13273,13 @@
         <v>22</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -13337,7 +13330,7 @@
         <v>22</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -13357,14 +13350,14 @@
         <v>3</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
@@ -13386,13 +13379,13 @@
         <v>127</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -13442,7 +13435,7 @@
         <v>22</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
@@ -13462,14 +13455,14 @@
         <v>3</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" t="s" s="2">
@@ -13491,16 +13484,16 @@
         <v>127</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P108" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>22</v>
@@ -13549,7 +13542,7 @@
         <v>22</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -13569,10 +13562,10 @@
         <v>3</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13595,17 +13588,17 @@
         <v>22</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Q109" t="s" s="2">
         <v>22</v>
@@ -13630,14 +13623,14 @@
         <v>22</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AA109" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AB109" t="s" s="2">
         <v>22</v>
       </c>
@@ -13654,7 +13647,7 @@
         <v>22</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>76</v>
@@ -13674,10 +13667,10 @@
         <v>3</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13700,17 +13693,17 @@
         <v>22</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q110" t="s" s="2">
         <v>22</v>
@@ -13759,7 +13752,7 @@
         <v>22</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -13779,10 +13772,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -13805,19 +13798,19 @@
         <v>22</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="P111" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q111" t="s" s="2">
         <v>22</v>
@@ -13866,7 +13859,7 @@
         <v>22</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13886,10 +13879,10 @@
         <v>3</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -13912,17 +13905,17 @@
         <v>22</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>22</v>
@@ -13971,7 +13964,7 @@
         <v>22</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>76</v>
@@ -13991,10 +13984,10 @@
         <v>3</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14020,14 +14013,14 @@
         <v>104</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q113" t="s" s="2">
         <v>22</v>
@@ -14052,13 +14045,13 @@
         <v>22</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AA113" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AB113" t="s" s="2">
         <v>22</v>
@@ -14076,7 +14069,7 @@
         <v>22</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>76</v>
@@ -14096,10 +14089,10 @@
         <v>3</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -14122,17 +14115,17 @@
         <v>22</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q114" t="s" s="2">
         <v>22</v>
@@ -14181,7 +14174,7 @@
         <v>22</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>76</v>
@@ -14190,7 +14183,7 @@
         <v>84</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>96</v>
@@ -14201,10 +14194,10 @@
         <v>3</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -14227,13 +14220,13 @@
         <v>22</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
@@ -14284,7 +14277,7 @@
         <v>22</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>76</v>
@@ -14304,10 +14297,10 @@
         <v>3</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14330,19 +14323,19 @@
         <v>22</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M116" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="P116" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>22</v>
@@ -14391,7 +14384,7 @@
         <v>22</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>76</v>
@@ -14411,10 +14404,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14437,13 +14430,13 @@
         <v>22</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -14494,7 +14487,7 @@
         <v>22</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>76</v>
@@ -14514,14 +14507,14 @@
         <v>3</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" t="s" s="2">
@@ -14543,13 +14536,13 @@
         <v>127</v>
       </c>
       <c r="M118" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N118" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P118" s="2"/>
       <c r="Q118" t="s" s="2">
@@ -14599,7 +14592,7 @@
         <v>22</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>76</v>
@@ -14619,14 +14612,14 @@
         <v>3</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
@@ -14648,16 +14641,16 @@
         <v>127</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P119" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q119" t="s" s="2">
         <v>22</v>
@@ -14706,7 +14699,7 @@
         <v>22</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -14726,10 +14719,10 @@
         <v>3</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -14752,19 +14745,19 @@
         <v>22</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M120" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="O120" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="P120" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="Q120" t="s" s="2">
         <v>22</v>
@@ -14789,13 +14782,13 @@
         <v>22</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z120" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AA120" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AB120" t="s" s="2">
         <v>22</v>
@@ -14813,7 +14806,7 @@
         <v>22</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>84</v>
@@ -14833,10 +14826,10 @@
         <v>3</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -14859,13 +14852,13 @@
         <v>22</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -14916,7 +14909,7 @@
         <v>22</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>76</v>
@@ -14936,14 +14929,14 @@
         <v>3</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" t="s" s="2">
@@ -14965,13 +14958,13 @@
         <v>127</v>
       </c>
       <c r="M122" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
@@ -15012,7 +15005,7 @@
         <v>130</v>
       </c>
       <c r="AD122" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE122" t="s" s="2">
         <v>22</v>
@@ -15021,7 +15014,7 @@
         <v>131</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>76</v>
@@ -15041,10 +15034,10 @@
         <v>3</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15067,19 +15060,19 @@
         <v>85</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="P123" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="Q123" t="s" s="2">
         <v>22</v>
@@ -15128,7 +15121,7 @@
         <v>22</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>76</v>
@@ -15148,10 +15141,10 @@
         <v>3</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15174,13 +15167,13 @@
         <v>22</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -15231,7 +15224,7 @@
         <v>22</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>76</v>
@@ -15251,14 +15244,14 @@
         <v>3</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" t="s" s="2">
@@ -15280,13 +15273,13 @@
         <v>127</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
@@ -15327,7 +15320,7 @@
         <v>130</v>
       </c>
       <c r="AD125" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AE125" t="s" s="2">
         <v>22</v>
@@ -15336,7 +15329,7 @@
         <v>131</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>76</v>
@@ -15356,10 +15349,10 @@
         <v>3</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15385,16 +15378,16 @@
         <v>98</v>
       </c>
       <c r="M126" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O126" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="P126" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="Q126" t="s" s="2">
         <v>22</v>
@@ -15443,7 +15436,7 @@
         <v>22</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>76</v>
@@ -15463,10 +15456,10 @@
         <v>3</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -15489,16 +15482,16 @@
         <v>85</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M127" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O127" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
@@ -15548,7 +15541,7 @@
         <v>22</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>76</v>
@@ -15568,10 +15561,10 @@
         <v>3</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -15597,14 +15590,14 @@
         <v>104</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>22</v>
@@ -15653,7 +15646,7 @@
         <v>22</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>76</v>
@@ -15673,10 +15666,10 @@
         <v>3</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -15699,17 +15692,17 @@
         <v>85</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>22</v>
@@ -15758,7 +15751,7 @@
         <v>22</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>76</v>
@@ -15778,10 +15771,10 @@
         <v>3</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -15804,19 +15797,19 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="P130" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="Q130" t="s" s="2">
         <v>22</v>
@@ -15865,7 +15858,7 @@
         <v>22</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>76</v>
@@ -15885,10 +15878,10 @@
         <v>3</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -15911,19 +15904,19 @@
         <v>85</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O131" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="P131" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>22</v>
@@ -15972,7 +15965,7 @@
         <v>22</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>76</v>
@@ -15992,10 +15985,10 @@
         <v>3</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16018,26 +16011,26 @@
         <v>22</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M132" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O132" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="P132" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>22</v>
       </c>
       <c r="R132" s="2"/>
       <c r="S132" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>22</v>
@@ -16079,7 +16072,7 @@
         <v>22</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>76</v>
@@ -16099,14 +16092,14 @@
         <v>3</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" t="s" s="2">
@@ -16125,16 +16118,16 @@
         <v>22</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -16184,7 +16177,7 @@
         <v>22</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>76</v>
@@ -16204,10 +16197,10 @@
         <v>3</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -16230,19 +16223,19 @@
         <v>85</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="M134" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="O134" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="P134" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="Q134" t="s" s="2">
         <v>22</v>
@@ -16291,7 +16284,7 @@
         <v>22</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>76</v>
@@ -16311,10 +16304,10 @@
         <v>3</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -16337,19 +16330,19 @@
         <v>85</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M135" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O135" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="P135" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="Q135" t="s" s="2">
         <v>22</v>
@@ -16398,7 +16391,7 @@
         <v>22</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>76</v>
@@ -16418,10 +16411,10 @@
         <v>3</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -16444,13 +16437,13 @@
         <v>22</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -16501,7 +16494,7 @@
         <v>22</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>76</v>
@@ -16521,14 +16514,14 @@
         <v>3</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
@@ -16550,13 +16543,13 @@
         <v>127</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
@@ -16606,7 +16599,7 @@
         <v>22</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>76</v>
@@ -16626,14 +16619,14 @@
         <v>3</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" t="s" s="2">
@@ -16655,16 +16648,16 @@
         <v>127</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P138" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q138" t="s" s="2">
         <v>22</v>
@@ -16713,7 +16706,7 @@
         <v>22</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>76</v>
@@ -16733,10 +16726,10 @@
         <v>3</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -16759,16 +16752,16 @@
         <v>85</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
@@ -16818,7 +16811,7 @@
         <v>22</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>84</v>
@@ -16838,10 +16831,10 @@
         <v>3</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -16867,10 +16860,10 @@
         <v>104</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -16897,13 +16890,13 @@
         <v>22</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AA140" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AB140" t="s" s="2">
         <v>22</v>
@@ -16921,7 +16914,7 @@
         <v>22</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>84</v>
